--- a/SuppXLS/Scen_UC_BIO_CEMENTHEAT_LO.xlsx
+++ b/SuppXLS/Scen_UC_BIO_CEMENTHEAT_LO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7047C0D9-325C-4F00-9CA8-AE467A410645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E866AD6-F160-4F2F-BB93-6E4AF951ADB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{58752476-08F6-480F-B14A-373304AB5756}"/>
   </bookViews>
@@ -622,7 +622,7 @@
         <v>1</v>
       </c>
       <c r="L6">
-        <v>-0.1</v>
+        <v>-0.15</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>-0.25</v>
+        <v>-0.3</v>
       </c>
       <c r="M7">
         <v>0</v>

--- a/SuppXLS/Scen_UC_BIO_CEMENTHEAT_LO.xlsx
+++ b/SuppXLS/Scen_UC_BIO_CEMENTHEAT_LO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E866AD6-F160-4F2F-BB93-6E4AF951ADB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB76F93-A67E-48CC-A74E-33815155DE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{58752476-08F6-480F-B14A-373304AB5756}"/>
   </bookViews>
@@ -622,7 +622,7 @@
         <v>1</v>
       </c>
       <c r="L6">
-        <v>-0.15</v>
+        <v>-0.1</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>-0.3</v>
+        <v>-0.15</v>
       </c>
       <c r="M7">
         <v>0</v>
